--- a/results/monthly_investor_report_2026-07-30.xlsx
+++ b/results/monthly_investor_report_2026-07-30.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -978,7 +978,7 @@
         <v>0.057165502871556</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>739.8365501968819</v>
+        <v>739.8365501968822</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>304.4636648270081</v>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1090027888193446</v>
+        <v>0.1090027888193445</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10900.27888193446</v>
+        <v>10900.27888193445</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>201.6529202696998</v>
+        <v>201.6529202696975</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>390.0854213272742</v>
+        <v>390.0854213272741</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>361.816597715633</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.334479855131823</v>
+        <v>0.3344798551318176</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>558.9610131012665</v>
+        <v>558.9610131012668</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>355.5735701074437</v>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08855294943930817</v>
+        <v>0.08855294943930818</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8855.294943930816</v>
+        <v>8855.294943930818</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0185280737323094</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.06864558375910687</v>
+        <v>0.0686455837591069</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6864.558375910687</v>
+        <v>6864.55837591069</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0238096245652548</v>
@@ -1153,7 +1153,7 @@
         <v>28.2992428565673</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.273293125713912</v>
+        <v>0.2732931257139113</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1509,7 +1509,7 @@
         <v>-0.0553091443456059</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.0814958906985057</v>
@@ -1518,7 +1518,7 @@
         <v>361.816597715633</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>390.0854213272742</v>
+        <v>390.0854213272741</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>414.2129261375277</v>
@@ -1563,10 +1563,10 @@
         <v>308.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.0557183387298561</v>
+        <v>-0.0557183387298559</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0063375475858378</v>
+        <v>0.0063375475858379</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>0.1846001644787691</v>
@@ -1626,7 +1626,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.1516948423836668</v>
+        <v>0.151694842383667</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1677,7 +1677,7 @@
         <v>42.40000152587891</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0603687366609073</v>
+        <v>-0.0603687366609074</v>
       </c>
       <c r="F12" s="22" t="n">
         <v>-0.0181817200022263</v>
@@ -1686,7 +1686,7 @@
         <v>0.0613532271160165</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>39.84036699934106</v>
+        <v>39.84036699934105</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>41.62909657004141</v>
@@ -1695,7 +1695,7 @@
         <v>45.0013784492156</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>39.84036699934106</v>
+        <v>39.84036699934105</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>191.5</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0083587415184747</v>
+        <v>-0.008358741518474801</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>0.0185280737323094</v>
@@ -1791,16 +1791,16 @@
         <v>101.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0616850558301536</v>
+        <v>-0.0616850558301534</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>-0.0232804071164443</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.0289375192237391</v>
+        <v>0.0289375192237388</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>95.2389668332394</v>
+        <v>95.23896683323943</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>99.13703867768091</v>
@@ -1809,7 +1809,7 @@
         <v>104.4371582012095</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>95.2389668332394</v>
+        <v>95.23896683323943</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>19.01000022888184</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>20.07129459190576</v>
+        <v>20.07129459190577</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>17.84444362991376</v>
@@ -1962,13 +1962,13 @@
         <v>31</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0871211981752482</v>
+        <v>-0.0871211981752484</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0.0238096245652548</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.0792951206779122</v>
+        <v>0.079295120677912</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -1977,7 +1977,7 @@
         <v>31.7380983615229</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>33.45814874101528</v>
+        <v>33.45814874101527</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2260,7 +2260,7 @@
         <v>0.020736118110066</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2303,7 @@
         <v>0.0216824464777646</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0063375475858378</v>
+        <v>0.0063375475858379</v>
       </c>
     </row>
     <row r="7">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0224080999198344</v>
+        <v>0.0224080999198345</v>
       </c>
       <c r="K10" s="22" t="n">
         <v>-0.0232804071164443</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0052328821703729</v>
+        <v>-0.0052328821703726</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.2340853963488951</v>
+        <v>-0.2340853963488949</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0439319706002252</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0261229653188725</v>
+        <v>0.0261229653188726</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>0.0050933786078097</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.0290376821986274</v>
+        <v>0.0290376821986273</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>0.0238096245652548</v>
@@ -2676,7 +2676,7 @@
         <v>-0.1440457436747242</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2066204726021715</v>
+        <v>-0.2066204726021714</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1007071692957457</v>
@@ -2716,7 +2716,7 @@
         <v>-0.0668171362404083</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>-0.08724310524054101</v>
+        <v>-0.0872431052405412</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.0061819138307206</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0253707760054063</v>
+        <v>0.0253707760054064</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0287515535773972</v>
@@ -2759,7 +2759,7 @@
         <v>-0.02466026155884</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.1371326901815062</v>
+        <v>-0.1371326901815061</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>-0.1499999866150972</v>
@@ -2805,7 +2805,7 @@
         <v>-0.1697376221065171</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.2523881271427706</v>
+        <v>-0.2523881271427707</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.0354464643980367</v>
@@ -2819,7 +2819,7 @@
         <v>0.0198916910720305</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.009701613552635499</v>
+        <v>0.0097016135526356</v>
       </c>
     </row>
     <row r="19">
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>-0.2000000198166092</v>
+        <v>-0.2000000198166093</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>-0.1641790905719934</v>
+        <v>-0.1641790905719935</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>-0.250744843998032</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0282262795302659</v>
+        <v>0.0282262795302658</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.0759492964836558</v>
@@ -2888,10 +2888,10 @@
         <v>-0.0928445395644775</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.2177461034064992</v>
+        <v>-0.2177461034064991</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2807583314076235</v>
+        <v>-0.2807583314076234</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1020340293017442</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0194542362354065</v>
+        <v>0.0194542362354064</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.1002252939750626</v>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report_2026-07-30.xlsx
+++ b/results/monthly_investor_report_2026-07-30.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report_2026-07-30.xlsx
+++ b/results/monthly_investor_report_2026-07-30.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1294201070633815</v>
+        <v>0.1294201302157204</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12942.01070633815</v>
+        <v>12942.01302157204</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>739.8365501968822</v>
+        <v>739.8370029028566</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>304.4636648270081</v>
+        <v>304.4636719558903</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8837659890840134</v>
+        <v>0.8837670800847366</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1090027888193445</v>
+        <v>0.1090028071327864</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10900.27888193445</v>
+        <v>10900.28071327864</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>201.6529202696975</v>
+        <v>201.6533089265887</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>390.0854213272741</v>
+        <v>390.0854337929846</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3344798551318176</v>
+        <v>0.3344805167966291</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1043785709188588</v>
+        <v>0.1043785775170885</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10437.85709188588</v>
+        <v>10437.85775170885</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0535513188368701</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>558.9610131012668</v>
+        <v>558.9610484356566</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>355.5735701074437</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08855294943930818</v>
+        <v>0.08855291398532347</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8855.294943930818</v>
+        <v>8855.291398532347</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>164.0715576424968</v>
+        <v>164.070445658855</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>195.0481261197373</v>
+        <v>195.0481034931135</v>
       </c>
       <c r="I23" s="8" t="n">
         <v>181.925</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.37056147464619</v>
+        <v>0.3705591115523262</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0686455837591069</v>
+        <v>0.06864557114908122</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6864.55837591069</v>
+        <v>6864.557114908122</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>163.4425577367087</v>
+        <v>163.4420738216836</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>31.7380983615229</v>
+        <v>31.7380963117735</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>28.2992428565673</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.2732931257139113</v>
+        <v>0.2732923667602955</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,25 +1449,25 @@
         <v>288</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0646839814811222</v>
+        <v>-0.064683929638042</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1505434775960539</v>
+        <v>0.1505434643863876</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>304.4636648270081</v>
+        <v>304.4636719558903</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>331.3565215476635</v>
+        <v>331.3565177432797</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
         <v>383</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0553091443456059</v>
+        <v>-0.0553091322415601</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.0814958906985057</v>
+        <v>0.0814962596984995</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>390.0854213272741</v>
+        <v>390.0854337929846</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>414.2129261375277</v>
+        <v>414.2130674645254</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1563,25 +1563,25 @@
         <v>308.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.0557183387298559</v>
+        <v>-0.0557185041218549</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0063375475858379</v>
+        <v>0.00633754713377</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.1846001644787691</v>
+        <v>0.1846002415757828</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>291.0748220865219</v>
+        <v>291.0747711044382</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>310.2035490433345</v>
+        <v>310.2035489039847</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>365.1530007005806</v>
+        <v>365.153024465735</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>291.0748220865219</v>
+        <v>291.0747711044382</v>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.151694842383667</v>
+        <v>0.1516950211453938</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1635,7 +1635,7 @@
         <v>355.5735701074437</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>388.6970093044876</v>
+        <v>388.6970696365704</v>
       </c>
       <c r="K11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1677,25 +1677,25 @@
         <v>42.40000152587891</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0603687366609074</v>
+        <v>-0.0603687118615568</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.0181817200022263</v>
+        <v>-0.0181818861523047</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0613532271160165</v>
+        <v>0.0613531469582715</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>39.84036699934105</v>
+        <v>39.84036805083355</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>41.62909657004141</v>
+        <v>41.62908952527783</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>45.0013784492156</v>
+        <v>45.00137505052709</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>39.84036699934105</v>
+        <v>39.84036805083355</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1734,22 +1734,22 @@
         <v>191.5</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.008358741518474801</v>
+        <v>-0.0083587023213938</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.0757753717076345</v>
+        <v>0.0757754432413195</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>189.8993009992121</v>
+        <v>189.8993085054531</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>195.0481261197373</v>
+        <v>195.0481034931135</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>206.010983682012</v>
+        <v>206.0109973807127</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>181.925</v>
@@ -1791,25 +1791,25 @@
         <v>101.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0616850558301534</v>
+        <v>-0.0616850558301536</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0232804071164443</v>
+        <v>-0.0232805184548855</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.0289375192237388</v>
+        <v>0.0289374356535263</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>95.23896683323943</v>
+        <v>95.2389668332394</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>99.13703867768091</v>
+        <v>99.13702737682912</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>104.4371582012095</v>
+        <v>104.4371497188329</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>95.23896683323943</v>
+        <v>95.2389668332394</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>19.01000022888184</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>20.07129459190577</v>
+        <v>20.07129459190576</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>17.84444362991376</v>
@@ -1905,25 +1905,25 @@
         <v>260.5</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.0713413812853959</v>
+        <v>-0.0713413679291167</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>0.0050933786078097</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.1023868619897293</v>
+        <v>0.1023869095225903</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>241.9155701751544</v>
+        <v>241.9155736544651</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>261.8268251273345</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>287.1717775483245</v>
+        <v>287.1717899306348</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>241.9155701751544</v>
+        <v>241.9155736544651</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -1962,22 +1962,22 @@
         <v>31</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0871211981752484</v>
+        <v>-0.0871211981752482</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.079295120677912</v>
+        <v>0.0792953142437882</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>28.2992428565673</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>31.7380983615229</v>
+        <v>31.7380963117735</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>33.45814874101527</v>
+        <v>33.45815474155744</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2217,7 +2217,7 @@
         <v>0.0240855922651444</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
     </row>
     <row r="5">
@@ -2260,7 +2260,7 @@
         <v>0.020736118110066</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
     </row>
     <row r="6">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.0216824464777646</v>
+        <v>0.0216824464777645</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0063375475858379</v>
+        <v>0.00633754713377</v>
       </c>
     </row>
     <row r="7">
@@ -2389,7 +2389,7 @@
         <v>0.0278304305933973</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>-0.0181817200022263</v>
+        <v>-0.0181818861523047</v>
       </c>
     </row>
     <row r="9">
@@ -2432,7 +2432,7 @@
         <v>0.0208004752934908</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
     </row>
     <row r="10">
@@ -2475,7 +2475,7 @@
         <v>0.0224080999198345</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>-0.0232804071164443</v>
+        <v>-0.0232805184548855</v>
       </c>
     </row>
     <row r="11">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0052328821703726</v>
+        <v>-0.0052328821703729</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.2340853963488949</v>
+        <v>-0.2340853963488951</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0439319706002252</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0261229653188726</v>
+        <v>0.0261229653188725</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>0.0050933786078097</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.0290376821986273</v>
+        <v>0.0290376821986274</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
     </row>
     <row r="14">
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="J14" s="27" t="n">
-        <v>0.0221556678262782</v>
+        <v>0.0221556678262783</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0156794711232165</v>
+        <v>0.0156795465450354</v>
       </c>
     </row>
     <row r="15">
@@ -2676,7 +2676,7 @@
         <v>-0.1440457436747242</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2066204726021714</v>
+        <v>-0.2066204726021715</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1007071692957457</v>
@@ -2716,7 +2716,7 @@
         <v>-0.0668171362404083</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>-0.0872431052405412</v>
+        <v>-0.08724310524054101</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.0061819138307206</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0253707760054064</v>
+        <v>0.0253707760054063</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0287515535773972</v>
@@ -2759,7 +2759,7 @@
         <v>-0.02466026155884</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.1371326901815061</v>
+        <v>-0.1371326901815062</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>-0.1499999866150972</v>
@@ -2776,7 +2776,7 @@
         <v>0.015715253363987</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.1196572591075438</v>
+        <v>0.1196572855882683</v>
       </c>
     </row>
     <row r="18">
@@ -2805,7 +2805,7 @@
         <v>-0.1697376221065171</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.2523881271427707</v>
+        <v>-0.2523881271427706</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.0354464643980367</v>
@@ -2819,7 +2819,7 @@
         <v>0.0198916910720305</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0097016135526356</v>
+        <v>0.009701613552635499</v>
       </c>
     </row>
     <row r="19">
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>-0.2000000198166093</v>
+        <v>-0.2000000198166092</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>-0.1641790905719935</v>
+        <v>-0.1641790905719934</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>-0.250744843998032</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0282262795302658</v>
+        <v>0.0282262795302659</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.0759492964836558</v>
@@ -2888,10 +2888,10 @@
         <v>-0.0928445395644775</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.2177461034064991</v>
+        <v>-0.2177461034064992</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2807583314076234</v>
+        <v>-0.2807583314076235</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1020340293017442</v>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0194542362354064</v>
+        <v>0.0194542362354065</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.1002252939750626</v>
+        <v>0.1002252058410154</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
